--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260728_210005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260728_210005.xlsx
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260728_210005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260728_210005.xlsx
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260728_210005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260728_210005.xlsx
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260728_210005.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260728_210005.xlsx
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
